--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -1744,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713595</v>
+        <v>119713560</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>87406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,21 +1760,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463728</v>
+        <v>463750</v>
       </c>
       <c r="R12" t="n">
-        <v>7079602</v>
+        <v>7079623</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713563</v>
+        <v>119713598</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>90558</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463821</v>
+        <v>463702</v>
       </c>
       <c r="R13" t="n">
-        <v>7079575</v>
+        <v>7079478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713598</v>
+        <v>119713595</v>
       </c>
       <c r="B14" t="n">
-        <v>90558</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463702</v>
+        <v>463728</v>
       </c>
       <c r="R14" t="n">
-        <v>7079478</v>
+        <v>7079602</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713560</v>
+        <v>119713591</v>
       </c>
       <c r="B15" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,21 +2066,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463750</v>
+        <v>463851</v>
       </c>
       <c r="R15" t="n">
-        <v>7079623</v>
+        <v>7079576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,6 +2126,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2152,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713591</v>
+        <v>119713575</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2192,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463851</v>
+        <v>463549</v>
       </c>
       <c r="R16" t="n">
-        <v>7079576</v>
+        <v>7079647</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,7 +2237,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2259,7 +2264,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713575</v>
+        <v>119713584</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2299,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463549</v>
+        <v>463721</v>
       </c>
       <c r="R17" t="n">
-        <v>7079647</v>
+        <v>7079654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2344,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713584</v>
+        <v>119713578</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2406,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463721</v>
+        <v>463582</v>
       </c>
       <c r="R18" t="n">
-        <v>7079654</v>
+        <v>7079667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2446,7 +2451,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2473,10 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713578</v>
+        <v>119713563</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,21 +2494,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,10 +2518,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463582</v>
+        <v>463821</v>
       </c>
       <c r="R19" t="n">
-        <v>7079667</v>
+        <v>7079575</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,11 +2554,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713596</v>
+        <v>119713571</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463751</v>
+        <v>463594</v>
       </c>
       <c r="R3" t="n">
-        <v>7079627</v>
+        <v>7079554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713571</v>
+        <v>119713569</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -935,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463594</v>
+        <v>463664</v>
       </c>
       <c r="R4" t="n">
-        <v>7079554</v>
+        <v>7079492</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713569</v>
+        <v>119713570</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,16 +1041,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463664</v>
+        <v>463587</v>
       </c>
       <c r="R5" t="n">
-        <v>7079492</v>
+        <v>7079621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713570</v>
+        <v>119713583</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1143,24 +1156,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463587</v>
+        <v>463715</v>
       </c>
       <c r="R6" t="n">
-        <v>7079621</v>
+        <v>7079654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Såg rätt nytt ut.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713583</v>
+        <v>119713596</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463715</v>
+        <v>463751</v>
       </c>
       <c r="R7" t="n">
-        <v>7079654</v>
+        <v>7079627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713592</v>
+        <v>119713567</v>
       </c>
       <c r="B2" t="n">
-        <v>56522</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,54 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463653</v>
+        <v>463736</v>
       </c>
       <c r="R2" t="n">
-        <v>7079415</v>
+        <v>7079409</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713571</v>
+        <v>119713573</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -833,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463594</v>
+        <v>463554</v>
       </c>
       <c r="R3" t="n">
-        <v>7079554</v>
+        <v>7079655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713569</v>
+        <v>119713563</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463664</v>
+        <v>463821</v>
       </c>
       <c r="R4" t="n">
-        <v>7079492</v>
+        <v>7079575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713570</v>
+        <v>119713600</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463587</v>
+        <v>463554</v>
       </c>
       <c r="R5" t="n">
-        <v>7079621</v>
+        <v>7079685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713583</v>
+        <v>119713602</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463715</v>
+        <v>463691</v>
       </c>
       <c r="R6" t="n">
-        <v>7079654</v>
+        <v>7079539</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1331,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713603</v>
+        <v>119713568</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463681</v>
+        <v>463727</v>
       </c>
       <c r="R8" t="n">
-        <v>7079627</v>
+        <v>7079425</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713605</v>
+        <v>119713579</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463787</v>
+        <v>463762</v>
       </c>
       <c r="R9" t="n">
-        <v>7079575</v>
+        <v>7079557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713573</v>
+        <v>119713572</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1575,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463554</v>
+        <v>463687</v>
       </c>
       <c r="R10" t="n">
-        <v>7079655</v>
+        <v>7079358</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1591,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713599</v>
+        <v>119713604</v>
       </c>
       <c r="B11" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463627</v>
+        <v>463710</v>
       </c>
       <c r="R11" t="n">
-        <v>7079516</v>
+        <v>7079569</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713560</v>
+        <v>119713578</v>
       </c>
       <c r="B12" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463750</v>
+        <v>463582</v>
       </c>
       <c r="R12" t="n">
-        <v>7079623</v>
+        <v>7079667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713598</v>
+        <v>119713581</v>
       </c>
       <c r="B13" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463702</v>
+        <v>463703</v>
       </c>
       <c r="R13" t="n">
-        <v>7079478</v>
+        <v>7079654</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,6 +1903,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713595</v>
+        <v>119713564</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463728</v>
+        <v>463698</v>
       </c>
       <c r="R14" t="n">
-        <v>7079602</v>
+        <v>7079631</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2050,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713591</v>
+        <v>119713582</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2090,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463851</v>
+        <v>463720</v>
       </c>
       <c r="R15" t="n">
-        <v>7079576</v>
+        <v>7079650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2157,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713575</v>
+        <v>119713606</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>86878</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463549</v>
+        <v>463502</v>
       </c>
       <c r="R16" t="n">
-        <v>7079647</v>
+        <v>7079603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,11 +2224,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713584</v>
+        <v>119713580</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2304,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463721</v>
+        <v>463737</v>
       </c>
       <c r="R17" t="n">
-        <v>7079654</v>
+        <v>7079612</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713578</v>
+        <v>119713592</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>56522</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,38 +2369,54 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463582</v>
+        <v>463653</v>
       </c>
       <c r="R18" t="n">
-        <v>7079667</v>
+        <v>7079415</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,11 +2449,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2478,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713563</v>
+        <v>119713593</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,34 +2491,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463821</v>
+        <v>463736</v>
       </c>
       <c r="R19" t="n">
-        <v>7079575</v>
+        <v>7079601</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713565</v>
+        <v>119713595</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,21 +2605,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2620,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463746</v>
+        <v>463728</v>
       </c>
       <c r="R20" t="n">
-        <v>7079435</v>
+        <v>7079602</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,11 +2665,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713606</v>
+        <v>119713591</v>
       </c>
       <c r="B21" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2707,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2727,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463502</v>
+        <v>463851</v>
       </c>
       <c r="R21" t="n">
-        <v>7079603</v>
+        <v>7079576</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,6 +2767,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2789,7 +2798,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713566</v>
+        <v>119713577</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2829,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463735</v>
+        <v>463553</v>
       </c>
       <c r="R22" t="n">
-        <v>7079408</v>
+        <v>7079641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,7 +2878,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2896,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713593</v>
+        <v>119713565</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2912,46 +2921,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463736</v>
+        <v>463746</v>
       </c>
       <c r="R23" t="n">
-        <v>7079601</v>
+        <v>7079435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,6 +2981,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3010,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713567</v>
+        <v>119713598</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3026,21 +3028,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3050,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463736</v>
+        <v>463702</v>
       </c>
       <c r="R24" t="n">
-        <v>7079409</v>
+        <v>7079478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,11 +3088,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3117,10 +3114,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713604</v>
+        <v>119713599</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3133,21 +3130,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3157,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463710</v>
+        <v>463627</v>
       </c>
       <c r="R25" t="n">
-        <v>7079569</v>
+        <v>7079516</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713600</v>
+        <v>119713570</v>
       </c>
       <c r="B26" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,34 +3232,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463554</v>
+        <v>463587</v>
       </c>
       <c r="R26" t="n">
-        <v>7079685</v>
+        <v>7079621</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,6 +3300,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,10 +3331,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713597</v>
+        <v>119713562</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>90905</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3333,25 +3343,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3361,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463766</v>
+        <v>463821</v>
       </c>
       <c r="R27" t="n">
-        <v>7079580</v>
+        <v>7079575</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,6 +3415,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3423,7 +3434,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713581</v>
+        <v>119713590</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3463,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463703</v>
+        <v>463843</v>
       </c>
       <c r="R28" t="n">
-        <v>7079654</v>
+        <v>7079570</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,7 +3514,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3530,10 +3541,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713579</v>
+        <v>119713560</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3546,21 +3557,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3570,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463762</v>
+        <v>463750</v>
       </c>
       <c r="R29" t="n">
-        <v>7079557</v>
+        <v>7079623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,11 +3617,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3637,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713562</v>
+        <v>119713589</v>
       </c>
       <c r="B30" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3649,25 +3655,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3677,10 +3683,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463821</v>
+        <v>463830</v>
       </c>
       <c r="R30" t="n">
-        <v>7079575</v>
+        <v>7079579</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,13 +3721,17 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3750,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713568</v>
+        <v>119713571</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3780,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463727</v>
+        <v>463594</v>
       </c>
       <c r="R31" t="n">
-        <v>7079425</v>
+        <v>7079554</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3847,7 +3857,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713580</v>
+        <v>119713566</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3887,10 +3897,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463737</v>
+        <v>463735</v>
       </c>
       <c r="R32" t="n">
-        <v>7079612</v>
+        <v>7079408</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,7 +3964,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713590</v>
+        <v>119713575</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -3994,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463843</v>
+        <v>463549</v>
       </c>
       <c r="R33" t="n">
-        <v>7079570</v>
+        <v>7079647</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4034,7 +4044,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4061,10 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713561</v>
+        <v>119713603</v>
       </c>
       <c r="B34" t="n">
-        <v>87406</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,21 +4087,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4412</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4101,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463862</v>
+        <v>463681</v>
       </c>
       <c r="R34" t="n">
-        <v>7079556</v>
+        <v>7079627</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4163,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713564</v>
+        <v>119713601</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4179,21 +4189,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4203,10 +4213,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463698</v>
+        <v>463624</v>
       </c>
       <c r="R35" t="n">
-        <v>7079631</v>
+        <v>7079647</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4239,11 +4249,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4270,7 +4275,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119713577</v>
+        <v>119713584</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4310,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463553</v>
+        <v>463721</v>
       </c>
       <c r="R36" t="n">
-        <v>7079641</v>
+        <v>7079654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4350,7 +4355,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4377,7 +4382,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713582</v>
+        <v>119713583</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463720</v>
+        <v>463715</v>
       </c>
       <c r="R37" t="n">
-        <v>7079650</v>
+        <v>7079654</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4457,7 +4462,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4484,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119713601</v>
+        <v>119713561</v>
       </c>
       <c r="B38" t="n">
-        <v>90558</v>
+        <v>87406</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4500,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>4412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4524,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463624</v>
+        <v>463862</v>
       </c>
       <c r="R38" t="n">
-        <v>7079647</v>
+        <v>7079556</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,10 +4591,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119713589</v>
+        <v>119713605</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4602,21 +4607,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463830</v>
+        <v>463787</v>
       </c>
       <c r="R39" t="n">
-        <v>7079579</v>
+        <v>7079575</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4662,11 +4667,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4693,7 +4693,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119713572</v>
+        <v>119713569</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463687</v>
+        <v>463664</v>
       </c>
       <c r="R40" t="n">
-        <v>7079358</v>
+        <v>7079492</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,10 +4800,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713602</v>
+        <v>119713597</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4816,21 +4816,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463691</v>
+        <v>463766</v>
       </c>
       <c r="R41" t="n">
-        <v>7079539</v>
+        <v>7079580</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713567</v>
+        <v>119713563</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463736</v>
+        <v>463821</v>
       </c>
       <c r="R2" t="n">
-        <v>7079409</v>
+        <v>7079575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713573</v>
+        <v>119713600</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,7 +820,7 @@
         <v>463554</v>
       </c>
       <c r="R3" t="n">
-        <v>7079655</v>
+        <v>7079685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713563</v>
+        <v>119713602</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463821</v>
+        <v>463691</v>
       </c>
       <c r="R4" t="n">
-        <v>7079575</v>
+        <v>7079539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713600</v>
+        <v>119713567</v>
       </c>
       <c r="B5" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463554</v>
+        <v>463736</v>
       </c>
       <c r="R5" t="n">
-        <v>7079685</v>
+        <v>7079409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713602</v>
+        <v>119713573</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463691</v>
+        <v>463554</v>
       </c>
       <c r="R6" t="n">
-        <v>7079539</v>
+        <v>7079655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713564</v>
+        <v>119713606</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>86878</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463698</v>
+        <v>463502</v>
       </c>
       <c r="R14" t="n">
-        <v>7079631</v>
+        <v>7079603</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713582</v>
+        <v>119713564</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2081,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463720</v>
+        <v>463698</v>
       </c>
       <c r="R15" t="n">
-        <v>7079650</v>
+        <v>7079631</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2116,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713606</v>
+        <v>119713592</v>
       </c>
       <c r="B16" t="n">
-        <v>86878</v>
+        <v>56522</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,38 +2155,54 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463502</v>
+        <v>463653</v>
       </c>
       <c r="R16" t="n">
-        <v>7079603</v>
+        <v>7079415</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713580</v>
+        <v>119713593</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,34 +2277,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463737</v>
+        <v>463736</v>
       </c>
       <c r="R17" t="n">
-        <v>7079612</v>
+        <v>7079601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2349,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713592</v>
+        <v>119713580</v>
       </c>
       <c r="B18" t="n">
-        <v>56522</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,54 +2387,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463653</v>
+        <v>463737</v>
       </c>
       <c r="R18" t="n">
-        <v>7079415</v>
+        <v>7079612</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,6 +2451,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2475,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713593</v>
+        <v>119713582</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,46 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463736</v>
+        <v>463720</v>
       </c>
       <c r="R19" t="n">
-        <v>7079601</v>
+        <v>7079650</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,6 +2558,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3541,10 +3541,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713560</v>
+        <v>119713603</v>
       </c>
       <c r="B29" t="n">
-        <v>87406</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4412</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463750</v>
+        <v>463681</v>
       </c>
       <c r="R29" t="n">
-        <v>7079623</v>
+        <v>7079627</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713566</v>
+        <v>119713575</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463735</v>
+        <v>463549</v>
       </c>
       <c r="R32" t="n">
-        <v>7079408</v>
+        <v>7079647</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3964,7 +3964,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713575</v>
+        <v>119713566</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463549</v>
+        <v>463735</v>
       </c>
       <c r="R33" t="n">
-        <v>7079647</v>
+        <v>7079408</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4071,10 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713603</v>
+        <v>119713560</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>87406</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4087,21 +4087,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463681</v>
+        <v>463750</v>
       </c>
       <c r="R34" t="n">
-        <v>7079627</v>
+        <v>7079623</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713563</v>
+        <v>119713593</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463821</v>
+        <v>463736</v>
       </c>
       <c r="R2" t="n">
-        <v>7079575</v>
+        <v>7079601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713600</v>
+        <v>119713601</v>
       </c>
       <c r="B3" t="n">
         <v>90558</v>
@@ -817,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463554</v>
+        <v>463624</v>
       </c>
       <c r="R3" t="n">
-        <v>7079685</v>
+        <v>7079647</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713602</v>
+        <v>119713573</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463691</v>
+        <v>463554</v>
       </c>
       <c r="R4" t="n">
-        <v>7079539</v>
+        <v>7079655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713567</v>
+        <v>119713563</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463736</v>
+        <v>463821</v>
       </c>
       <c r="R5" t="n">
-        <v>7079409</v>
+        <v>7079575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713573</v>
+        <v>119713599</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463554</v>
+        <v>463627</v>
       </c>
       <c r="R6" t="n">
-        <v>7079655</v>
+        <v>7079516</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1176,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713596</v>
+        <v>119713602</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1218,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463751</v>
+        <v>463691</v>
       </c>
       <c r="R7" t="n">
-        <v>7079627</v>
+        <v>7079539</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1304,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713568</v>
+        <v>119713566</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1337,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463727</v>
+        <v>463735</v>
       </c>
       <c r="R8" t="n">
-        <v>7079425</v>
+        <v>7079408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1411,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713579</v>
+        <v>119713591</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1444,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463762</v>
+        <v>463851</v>
       </c>
       <c r="R9" t="n">
-        <v>7079557</v>
+        <v>7079576</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713572</v>
+        <v>119713580</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1551,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463687</v>
+        <v>463737</v>
       </c>
       <c r="R10" t="n">
-        <v>7079358</v>
+        <v>7079612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1598,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713604</v>
+        <v>119713596</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1641,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463710</v>
+        <v>463751</v>
       </c>
       <c r="R11" t="n">
-        <v>7079569</v>
+        <v>7079627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713578</v>
+        <v>119713605</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463582</v>
+        <v>463787</v>
       </c>
       <c r="R12" t="n">
-        <v>7079667</v>
+        <v>7079575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1803,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713581</v>
+        <v>119713560</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1845,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463703</v>
+        <v>463750</v>
       </c>
       <c r="R13" t="n">
-        <v>7079654</v>
+        <v>7079623</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,11 +1905,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713606</v>
+        <v>119713572</v>
       </c>
       <c r="B14" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1947,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463502</v>
+        <v>463687</v>
       </c>
       <c r="R14" t="n">
-        <v>7079603</v>
+        <v>7079358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2007,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,7 +2038,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713564</v>
+        <v>119713578</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2076,10 +2078,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463698</v>
+        <v>463582</v>
       </c>
       <c r="R15" t="n">
-        <v>7079631</v>
+        <v>7079667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,7 +2118,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713592</v>
+        <v>119713565</v>
       </c>
       <c r="B16" t="n">
-        <v>56522</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2155,54 +2157,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463653</v>
+        <v>463746</v>
       </c>
       <c r="R16" t="n">
-        <v>7079415</v>
+        <v>7079435</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,6 +2221,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713593</v>
+        <v>119713582</v>
       </c>
       <c r="B17" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,46 +2268,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463736</v>
+        <v>463720</v>
       </c>
       <c r="R17" t="n">
-        <v>7079601</v>
+        <v>7079650</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,6 +2328,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713580</v>
+        <v>119713600</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,21 +2375,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2415,10 +2399,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463737</v>
+        <v>463554</v>
       </c>
       <c r="R18" t="n">
-        <v>7079612</v>
+        <v>7079685</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,11 +2435,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2461,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713582</v>
+        <v>119713561</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2477,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463720</v>
+        <v>463862</v>
       </c>
       <c r="R19" t="n">
-        <v>7079650</v>
+        <v>7079556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,11 +2537,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713595</v>
+        <v>119713577</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,21 +2579,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2629,10 +2603,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463728</v>
+        <v>463553</v>
       </c>
       <c r="R20" t="n">
-        <v>7079602</v>
+        <v>7079641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,6 +2639,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713591</v>
+        <v>119713603</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2707,21 +2686,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2731,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463851</v>
+        <v>463681</v>
       </c>
       <c r="R21" t="n">
-        <v>7079576</v>
+        <v>7079627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,11 +2746,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,10 +2772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713577</v>
+        <v>119713604</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2814,21 +2788,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2838,10 +2812,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463553</v>
+        <v>463710</v>
       </c>
       <c r="R22" t="n">
-        <v>7079641</v>
+        <v>7079569</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,11 +2848,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2905,7 +2874,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713565</v>
+        <v>119713579</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2945,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463746</v>
+        <v>463762</v>
       </c>
       <c r="R23" t="n">
-        <v>7079435</v>
+        <v>7079557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,10 +2981,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713598</v>
+        <v>119713592</v>
       </c>
       <c r="B24" t="n">
-        <v>90558</v>
+        <v>56522</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,38 +2993,54 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463702</v>
+        <v>463653</v>
       </c>
       <c r="R24" t="n">
-        <v>7079478</v>
+        <v>7079415</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713599</v>
+        <v>119713589</v>
       </c>
       <c r="B25" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,21 +3115,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3154,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463627</v>
+        <v>463830</v>
       </c>
       <c r="R25" t="n">
-        <v>7079516</v>
+        <v>7079579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3190,6 +3175,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3216,7 +3206,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713570</v>
+        <v>119713583</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3250,24 +3240,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463587</v>
+        <v>463715</v>
       </c>
       <c r="R26" t="n">
-        <v>7079621</v>
+        <v>7079654</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,7 +3286,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Såg rätt nytt ut.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3331,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713562</v>
+        <v>119713595</v>
       </c>
       <c r="B27" t="n">
-        <v>90905</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,25 +3325,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463821</v>
+        <v>463728</v>
       </c>
       <c r="R27" t="n">
-        <v>7079575</v>
+        <v>7079602</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3397,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3434,10 +3415,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713590</v>
+        <v>119713597</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,21 +3431,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3474,10 +3455,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463843</v>
+        <v>463766</v>
       </c>
       <c r="R28" t="n">
-        <v>7079570</v>
+        <v>7079580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3510,11 +3491,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3541,10 +3517,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713603</v>
+        <v>119713590</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3557,21 +3533,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3581,10 +3557,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463681</v>
+        <v>463843</v>
       </c>
       <c r="R29" t="n">
-        <v>7079627</v>
+        <v>7079570</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3617,6 +3593,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3643,7 +3624,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713589</v>
+        <v>119713584</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3683,10 +3664,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463830</v>
+        <v>463721</v>
       </c>
       <c r="R30" t="n">
-        <v>7079579</v>
+        <v>7079654</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,7 +3704,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3750,7 +3731,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713571</v>
+        <v>119713564</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3790,10 +3771,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463594</v>
+        <v>463698</v>
       </c>
       <c r="R31" t="n">
-        <v>7079554</v>
+        <v>7079631</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713575</v>
+        <v>119713562</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,25 +3850,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3897,10 +3878,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463549</v>
+        <v>463821</v>
       </c>
       <c r="R32" t="n">
-        <v>7079647</v>
+        <v>7079575</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,17 +3916,13 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3964,7 +3941,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713566</v>
+        <v>119713575</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4004,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463735</v>
+        <v>463549</v>
       </c>
       <c r="R33" t="n">
-        <v>7079408</v>
+        <v>7079647</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,7 +4021,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4071,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713560</v>
+        <v>119713598</v>
       </c>
       <c r="B34" t="n">
-        <v>87406</v>
+        <v>90558</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4087,21 +4064,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4412</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4111,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463750</v>
+        <v>463702</v>
       </c>
       <c r="R34" t="n">
-        <v>7079623</v>
+        <v>7079478</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4150,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713601</v>
+        <v>119713567</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,21 +4166,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4213,10 +4190,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463624</v>
+        <v>463736</v>
       </c>
       <c r="R35" t="n">
-        <v>7079647</v>
+        <v>7079409</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,6 +4226,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4275,7 +4257,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119713584</v>
+        <v>119713581</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4315,7 +4297,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463721</v>
+        <v>463703</v>
       </c>
       <c r="R36" t="n">
         <v>7079654</v>
@@ -4382,7 +4364,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713583</v>
+        <v>119713570</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4416,16 +4398,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463715</v>
+        <v>463587</v>
       </c>
       <c r="R37" t="n">
-        <v>7079654</v>
+        <v>7079621</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4462,7 +4452,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4489,10 +4479,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119713561</v>
+        <v>119713568</v>
       </c>
       <c r="B38" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,21 +4495,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,10 +4519,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463862</v>
+        <v>463727</v>
       </c>
       <c r="R38" t="n">
-        <v>7079556</v>
+        <v>7079425</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,6 +4555,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4591,10 +4586,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119713605</v>
+        <v>119713571</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4607,21 +4602,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463787</v>
+        <v>463594</v>
       </c>
       <c r="R39" t="n">
-        <v>7079575</v>
+        <v>7079554</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4667,6 +4662,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4800,10 +4800,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713597</v>
+        <v>119713606</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>86878</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4816,21 +4816,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463766</v>
+        <v>463502</v>
       </c>
       <c r="R41" t="n">
-        <v>7079580</v>
+        <v>7079603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713598</v>
+        <v>119713567</v>
       </c>
       <c r="B34" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,21 +4064,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463702</v>
+        <v>463736</v>
       </c>
       <c r="R34" t="n">
-        <v>7079478</v>
+        <v>7079409</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4124,6 +4124,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4150,7 +4155,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713567</v>
+        <v>119713581</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4190,10 +4195,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463736</v>
+        <v>463703</v>
       </c>
       <c r="R35" t="n">
-        <v>7079409</v>
+        <v>7079654</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4230,7 +4235,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,7 +4262,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119713581</v>
+        <v>119713570</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4291,16 +4296,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463703</v>
+        <v>463587</v>
       </c>
       <c r="R36" t="n">
-        <v>7079654</v>
+        <v>7079621</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4337,7 +4350,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4364,10 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713570</v>
+        <v>119713598</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4380,42 +4393,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463587</v>
+        <v>463702</v>
       </c>
       <c r="R37" t="n">
-        <v>7079621</v>
+        <v>7079478</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4448,11 +4453,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713593</v>
+        <v>119713597</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463736</v>
+        <v>463766</v>
       </c>
       <c r="R2" t="n">
-        <v>7079601</v>
+        <v>7079580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713601</v>
+        <v>119713581</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463624</v>
+        <v>463703</v>
       </c>
       <c r="R3" t="n">
-        <v>7079647</v>
+        <v>7079654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713573</v>
+        <v>119713584</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -931,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463554</v>
+        <v>463721</v>
       </c>
       <c r="R4" t="n">
-        <v>7079655</v>
+        <v>7079654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713563</v>
+        <v>119713605</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,7 +1031,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463821</v>
+        <v>463787</v>
       </c>
       <c r="R5" t="n">
         <v>7079575</v>
@@ -1100,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713599</v>
+        <v>119713592</v>
       </c>
       <c r="B6" t="n">
-        <v>90558</v>
+        <v>56522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,38 +1105,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463627</v>
+        <v>463653</v>
       </c>
       <c r="R6" t="n">
-        <v>7079516</v>
+        <v>7079415</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713602</v>
+        <v>119713579</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1242,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463691</v>
+        <v>463762</v>
       </c>
       <c r="R7" t="n">
-        <v>7079539</v>
+        <v>7079557</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,6 +1287,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1318,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713566</v>
+        <v>119713583</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1344,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463735</v>
+        <v>463715</v>
       </c>
       <c r="R8" t="n">
-        <v>7079408</v>
+        <v>7079654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,7 +1398,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713591</v>
+        <v>119713593</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,34 +1441,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463851</v>
+        <v>463736</v>
       </c>
       <c r="R9" t="n">
-        <v>7079576</v>
+        <v>7079601</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,11 +1513,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713580</v>
+        <v>119713561</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463737</v>
+        <v>463862</v>
       </c>
       <c r="R10" t="n">
-        <v>7079612</v>
+        <v>7079556</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,11 +1615,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713596</v>
+        <v>119713590</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,21 +1657,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1665,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463751</v>
+        <v>463843</v>
       </c>
       <c r="R11" t="n">
-        <v>7079627</v>
+        <v>7079570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,6 +1717,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713605</v>
+        <v>119713570</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,34 +1764,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463787</v>
+        <v>463587</v>
       </c>
       <c r="R12" t="n">
-        <v>7079575</v>
+        <v>7079621</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,6 +1832,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713560</v>
+        <v>119713577</v>
       </c>
       <c r="B13" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,21 +1879,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463750</v>
+        <v>463553</v>
       </c>
       <c r="R13" t="n">
-        <v>7079623</v>
+        <v>7079641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,6 +1939,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,7 +1970,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713572</v>
+        <v>119713582</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1971,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463687</v>
+        <v>463720</v>
       </c>
       <c r="R14" t="n">
-        <v>7079358</v>
+        <v>7079650</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713578</v>
+        <v>119713598</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2054,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2078,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463582</v>
+        <v>463702</v>
       </c>
       <c r="R15" t="n">
-        <v>7079667</v>
+        <v>7079478</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,11 +2153,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713565</v>
+        <v>119713562</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,25 +2191,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463746</v>
+        <v>463821</v>
       </c>
       <c r="R16" t="n">
-        <v>7079435</v>
+        <v>7079575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,17 +2257,13 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2252,7 +2282,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713582</v>
+        <v>119713575</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2292,10 +2322,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463720</v>
+        <v>463549</v>
       </c>
       <c r="R17" t="n">
-        <v>7079650</v>
+        <v>7079647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713600</v>
+        <v>119713578</v>
       </c>
       <c r="B18" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,21 +2405,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2399,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463554</v>
+        <v>463582</v>
       </c>
       <c r="R18" t="n">
-        <v>7079685</v>
+        <v>7079667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,6 +2465,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2461,10 +2496,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713561</v>
+        <v>119713600</v>
       </c>
       <c r="B19" t="n">
-        <v>87406</v>
+        <v>90558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2477,21 +2512,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4412</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2501,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463862</v>
+        <v>463554</v>
       </c>
       <c r="R19" t="n">
-        <v>7079556</v>
+        <v>7079685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2598,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713577</v>
+        <v>119713565</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2603,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463553</v>
+        <v>463746</v>
       </c>
       <c r="R20" t="n">
-        <v>7079641</v>
+        <v>7079435</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,7 +2678,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2670,10 +2705,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713603</v>
+        <v>119713596</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,21 +2721,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2710,7 +2745,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463681</v>
+        <v>463751</v>
       </c>
       <c r="R21" t="n">
         <v>7079627</v>
@@ -2772,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713604</v>
+        <v>119713566</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,21 +2823,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2812,10 +2847,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463710</v>
+        <v>463735</v>
       </c>
       <c r="R22" t="n">
-        <v>7079569</v>
+        <v>7079408</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2848,6 +2883,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2874,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713579</v>
+        <v>119713602</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,21 +2930,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2914,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463762</v>
+        <v>463691</v>
       </c>
       <c r="R23" t="n">
-        <v>7079557</v>
+        <v>7079539</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,11 +2990,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2981,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713592</v>
+        <v>119713606</v>
       </c>
       <c r="B24" t="n">
-        <v>56522</v>
+        <v>86878</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2993,54 +3028,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463653</v>
+        <v>463502</v>
       </c>
       <c r="R24" t="n">
-        <v>7079415</v>
+        <v>7079603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713589</v>
+        <v>119713595</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3115,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463830</v>
+        <v>463728</v>
       </c>
       <c r="R25" t="n">
-        <v>7079579</v>
+        <v>7079602</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3175,11 +3194,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3206,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713583</v>
+        <v>119713568</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3246,10 +3260,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463715</v>
+        <v>463727</v>
       </c>
       <c r="R26" t="n">
-        <v>7079654</v>
+        <v>7079425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3286,7 +3300,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3313,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713595</v>
+        <v>119713572</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3329,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3353,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463728</v>
+        <v>463687</v>
       </c>
       <c r="R27" t="n">
-        <v>7079602</v>
+        <v>7079358</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3389,6 +3403,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3415,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713597</v>
+        <v>119713567</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3431,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3455,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463766</v>
+        <v>463736</v>
       </c>
       <c r="R28" t="n">
-        <v>7079580</v>
+        <v>7079409</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3491,6 +3510,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3517,7 +3541,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713590</v>
+        <v>119713580</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3557,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463843</v>
+        <v>463737</v>
       </c>
       <c r="R29" t="n">
-        <v>7079570</v>
+        <v>7079612</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3597,7 +3621,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3624,7 +3648,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713584</v>
+        <v>119713564</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3664,10 +3688,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463721</v>
+        <v>463698</v>
       </c>
       <c r="R30" t="n">
-        <v>7079654</v>
+        <v>7079631</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3755,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713564</v>
+        <v>119713569</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3771,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463698</v>
+        <v>463664</v>
       </c>
       <c r="R31" t="n">
-        <v>7079631</v>
+        <v>7079492</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,10 +3862,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713562</v>
+        <v>119713560</v>
       </c>
       <c r="B32" t="n">
-        <v>90905</v>
+        <v>87406</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,25 +3874,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3878,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463821</v>
+        <v>463750</v>
       </c>
       <c r="R32" t="n">
-        <v>7079575</v>
+        <v>7079623</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3922,7 +3946,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3941,10 +3964,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713575</v>
+        <v>119713563</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3981,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463549</v>
+        <v>463821</v>
       </c>
       <c r="R33" t="n">
-        <v>7079647</v>
+        <v>7079575</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4017,11 +4040,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,10 +4066,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713567</v>
+        <v>119713599</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,21 +4082,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4106,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463736</v>
+        <v>463627</v>
       </c>
       <c r="R34" t="n">
-        <v>7079409</v>
+        <v>7079516</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4124,11 +4142,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,7 +4168,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713581</v>
+        <v>119713573</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4195,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463703</v>
+        <v>463554</v>
       </c>
       <c r="R35" t="n">
-        <v>7079654</v>
+        <v>7079655</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4262,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119713570</v>
+        <v>119713601</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4278,42 +4291,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463587</v>
+        <v>463624</v>
       </c>
       <c r="R36" t="n">
-        <v>7079621</v>
+        <v>7079647</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4346,11 +4351,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4377,10 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713598</v>
+        <v>119713603</v>
       </c>
       <c r="B37" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463702</v>
+        <v>463681</v>
       </c>
       <c r="R37" t="n">
-        <v>7079478</v>
+        <v>7079627</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,7 +4479,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119713568</v>
+        <v>119713591</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463727</v>
+        <v>463851</v>
       </c>
       <c r="R38" t="n">
-        <v>7079425</v>
+        <v>7079576</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119713569</v>
+        <v>119713589</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463664</v>
+        <v>463830</v>
       </c>
       <c r="R40" t="n">
-        <v>7079492</v>
+        <v>7079579</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,10 +4800,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713606</v>
+        <v>119713604</v>
       </c>
       <c r="B41" t="n">
-        <v>86878</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4816,21 +4816,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463502</v>
+        <v>463710</v>
       </c>
       <c r="R41" t="n">
-        <v>7079603</v>
+        <v>7079569</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713606</v>
+        <v>119713595</v>
       </c>
       <c r="B24" t="n">
-        <v>86878</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463502</v>
+        <v>463728</v>
       </c>
       <c r="R24" t="n">
-        <v>7079603</v>
+        <v>7079602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713595</v>
+        <v>119713606</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>86878</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463728</v>
+        <v>463502</v>
       </c>
       <c r="R25" t="n">
-        <v>7079602</v>
+        <v>7079603</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713595</v>
+        <v>119713606</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>86878</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463728</v>
+        <v>463502</v>
       </c>
       <c r="R24" t="n">
-        <v>7079602</v>
+        <v>7079603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713606</v>
+        <v>119713595</v>
       </c>
       <c r="B25" t="n">
-        <v>86878</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463502</v>
+        <v>463728</v>
       </c>
       <c r="R25" t="n">
-        <v>7079603</v>
+        <v>7079602</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -3434,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713567</v>
+        <v>119713560</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463736</v>
+        <v>463750</v>
       </c>
       <c r="R28" t="n">
-        <v>7079409</v>
+        <v>7079623</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3510,11 +3510,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3541,7 +3536,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713580</v>
+        <v>119713567</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3581,10 +3576,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463737</v>
+        <v>463736</v>
       </c>
       <c r="R29" t="n">
-        <v>7079612</v>
+        <v>7079409</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,7 +3616,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3648,7 +3643,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713564</v>
+        <v>119713580</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3688,10 +3683,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463698</v>
+        <v>463737</v>
       </c>
       <c r="R30" t="n">
-        <v>7079631</v>
+        <v>7079612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,7 +3750,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713569</v>
+        <v>119713564</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3795,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463664</v>
+        <v>463698</v>
       </c>
       <c r="R31" t="n">
-        <v>7079492</v>
+        <v>7079631</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,10 +3857,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713560</v>
+        <v>119713569</v>
       </c>
       <c r="B32" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3878,21 +3873,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3902,10 +3897,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463750</v>
+        <v>463664</v>
       </c>
       <c r="R32" t="n">
-        <v>7079623</v>
+        <v>7079492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3938,6 +3933,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713563</v>
+        <v>119713573</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3980,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463821</v>
+        <v>463554</v>
       </c>
       <c r="R33" t="n">
-        <v>7079575</v>
+        <v>7079655</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4040,6 +4040,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,10 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713599</v>
+        <v>119713563</v>
       </c>
       <c r="B34" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4082,21 +4087,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4106,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463627</v>
+        <v>463821</v>
       </c>
       <c r="R34" t="n">
-        <v>7079516</v>
+        <v>7079575</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4168,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713573</v>
+        <v>119713599</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4184,21 +4189,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4208,10 +4213,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463554</v>
+        <v>463627</v>
       </c>
       <c r="R35" t="n">
-        <v>7079655</v>
+        <v>7079516</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,11 +4249,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713595</v>
+        <v>119713606</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>86878</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463728</v>
+        <v>463502</v>
       </c>
       <c r="R24" t="n">
-        <v>7079602</v>
+        <v>7079603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713606</v>
+        <v>119713595</v>
       </c>
       <c r="B25" t="n">
-        <v>86878</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463502</v>
+        <v>463728</v>
       </c>
       <c r="R25" t="n">
-        <v>7079603</v>
+        <v>7079602</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713560</v>
+        <v>119713567</v>
       </c>
       <c r="B28" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463750</v>
+        <v>463736</v>
       </c>
       <c r="R28" t="n">
-        <v>7079623</v>
+        <v>7079409</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3510,6 +3510,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3536,7 +3541,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713567</v>
+        <v>119713580</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3576,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463736</v>
+        <v>463737</v>
       </c>
       <c r="R29" t="n">
-        <v>7079409</v>
+        <v>7079612</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3616,7 +3621,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3643,7 +3648,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713580</v>
+        <v>119713564</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3683,10 +3688,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463737</v>
+        <v>463698</v>
       </c>
       <c r="R30" t="n">
-        <v>7079612</v>
+        <v>7079631</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3755,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713564</v>
+        <v>119713569</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3790,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463698</v>
+        <v>463664</v>
       </c>
       <c r="R31" t="n">
-        <v>7079631</v>
+        <v>7079492</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3862,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713569</v>
+        <v>119713560</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3878,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3897,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463664</v>
+        <v>463750</v>
       </c>
       <c r="R32" t="n">
-        <v>7079492</v>
+        <v>7079623</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,11 +3938,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 32351-2024 artfynd.xlsx
+++ b/artfynd/A 32351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713597</v>
+        <v>119713600</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>90576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463766</v>
+        <v>463554</v>
       </c>
       <c r="R2" t="n">
-        <v>7079580</v>
+        <v>7079685</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713581</v>
+        <v>119713595</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463703</v>
+        <v>463728</v>
       </c>
       <c r="R3" t="n">
-        <v>7079654</v>
+        <v>7079602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713584</v>
+        <v>119713569</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463721</v>
+        <v>463664</v>
       </c>
       <c r="R4" t="n">
-        <v>7079654</v>
+        <v>7079492</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713605</v>
+        <v>119713571</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463787</v>
+        <v>463594</v>
       </c>
       <c r="R5" t="n">
-        <v>7079575</v>
+        <v>7079554</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713592</v>
+        <v>119713581</v>
       </c>
       <c r="B6" t="n">
-        <v>56522</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,54 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463653</v>
+        <v>463703</v>
       </c>
       <c r="R6" t="n">
-        <v>7079415</v>
+        <v>7079654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713579</v>
+        <v>119713597</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463762</v>
+        <v>463766</v>
       </c>
       <c r="R7" t="n">
-        <v>7079557</v>
+        <v>7079580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713583</v>
+        <v>119713573</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463715</v>
+        <v>463554</v>
       </c>
       <c r="R8" t="n">
-        <v>7079654</v>
+        <v>7079655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713593</v>
+        <v>119713570</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,46 +1425,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463736</v>
+        <v>463587</v>
       </c>
       <c r="R9" t="n">
-        <v>7079601</v>
+        <v>7079621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713561</v>
+        <v>119713577</v>
       </c>
       <c r="B10" t="n">
-        <v>87406</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463862</v>
+        <v>463553</v>
       </c>
       <c r="R10" t="n">
-        <v>7079556</v>
+        <v>7079641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,6 +1600,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713590</v>
+        <v>119713562</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90923</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,25 +1643,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463843</v>
+        <v>463821</v>
       </c>
       <c r="R11" t="n">
-        <v>7079570</v>
+        <v>7079575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,17 +1709,13 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713570</v>
+        <v>119713606</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>86895</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,42 +1750,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463587</v>
+        <v>463502</v>
       </c>
       <c r="R12" t="n">
-        <v>7079621</v>
+        <v>7079603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,11 +1810,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Såg rätt nytt ut.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713577</v>
+        <v>119713605</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1903,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463553</v>
+        <v>463787</v>
       </c>
       <c r="R13" t="n">
-        <v>7079641</v>
+        <v>7079575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,11 +1912,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713582</v>
+        <v>119713560</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>87423</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,21 +1954,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463720</v>
+        <v>463750</v>
       </c>
       <c r="R14" t="n">
-        <v>7079650</v>
+        <v>7079623</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,11 +2014,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713598</v>
+        <v>119713566</v>
       </c>
       <c r="B15" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463702</v>
+        <v>463735</v>
       </c>
       <c r="R15" t="n">
-        <v>7079478</v>
+        <v>7079408</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,6 +2116,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119713562</v>
+        <v>119713598</v>
       </c>
       <c r="B16" t="n">
-        <v>90905</v>
+        <v>90576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,25 +2159,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463821</v>
+        <v>463702</v>
       </c>
       <c r="R16" t="n">
-        <v>7079575</v>
+        <v>7079478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2231,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2282,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119713575</v>
+        <v>119713604</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,21 +2265,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463549</v>
+        <v>463710</v>
       </c>
       <c r="R17" t="n">
-        <v>7079647</v>
+        <v>7079569</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,11 +2325,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,10 +2351,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713578</v>
+        <v>119713591</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,10 +2391,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463582</v>
+        <v>463851</v>
       </c>
       <c r="R18" t="n">
-        <v>7079667</v>
+        <v>7079576</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,7 +2431,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2496,10 +2458,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119713600</v>
+        <v>119713575</v>
       </c>
       <c r="B19" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2512,21 +2474,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2536,10 +2498,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463554</v>
+        <v>463549</v>
       </c>
       <c r="R19" t="n">
-        <v>7079685</v>
+        <v>7079647</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,6 +2534,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,10 +2565,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713565</v>
+        <v>119713583</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2638,10 +2605,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463746</v>
+        <v>463715</v>
       </c>
       <c r="R20" t="n">
-        <v>7079435</v>
+        <v>7079654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2645,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119713596</v>
+        <v>119713582</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,21 +2688,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2745,10 +2712,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463751</v>
+        <v>463720</v>
       </c>
       <c r="R21" t="n">
-        <v>7079627</v>
+        <v>7079650</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,6 +2748,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2807,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119713566</v>
+        <v>119713599</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2823,21 +2795,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2847,10 +2819,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463735</v>
+        <v>463627</v>
       </c>
       <c r="R22" t="n">
-        <v>7079408</v>
+        <v>7079516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,11 +2855,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2914,10 +2881,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119713602</v>
+        <v>119713603</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2954,10 +2921,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463691</v>
+        <v>463681</v>
       </c>
       <c r="R23" t="n">
-        <v>7079539</v>
+        <v>7079627</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119713595</v>
+        <v>119713580</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +2999,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3023,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463728</v>
+        <v>463737</v>
       </c>
       <c r="R24" t="n">
-        <v>7079602</v>
+        <v>7079612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,6 +3059,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,10 +3090,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119713606</v>
+        <v>119713590</v>
       </c>
       <c r="B25" t="n">
-        <v>86878</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3106,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3130,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463502</v>
+        <v>463843</v>
       </c>
       <c r="R25" t="n">
-        <v>7079603</v>
+        <v>7079570</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,6 +3166,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3220,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713568</v>
+        <v>119713564</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463727</v>
+        <v>463698</v>
       </c>
       <c r="R26" t="n">
-        <v>7079425</v>
+        <v>7079631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,10 +3304,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713572</v>
+        <v>119713568</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,10 +3344,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463687</v>
+        <v>463727</v>
       </c>
       <c r="R27" t="n">
-        <v>7079358</v>
+        <v>7079425</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3407,7 +3384,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3434,10 +3411,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119713567</v>
+        <v>119713592</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>56532</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,38 +3423,54 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463736</v>
+        <v>463653</v>
       </c>
       <c r="R28" t="n">
-        <v>7079409</v>
+        <v>7079415</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3510,11 +3503,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3541,10 +3529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119713580</v>
+        <v>119713589</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3581,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463737</v>
+        <v>463830</v>
       </c>
       <c r="R29" t="n">
-        <v>7079612</v>
+        <v>7079579</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,7 +3609,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3648,10 +3636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119713564</v>
+        <v>119713561</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>87423</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3664,21 +3652,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3688,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463698</v>
+        <v>463862</v>
       </c>
       <c r="R30" t="n">
-        <v>7079631</v>
+        <v>7079556</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3724,11 +3712,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3755,10 +3738,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119713569</v>
+        <v>119713563</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,21 +3754,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3795,10 +3778,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463664</v>
+        <v>463821</v>
       </c>
       <c r="R31" t="n">
-        <v>7079492</v>
+        <v>7079575</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3831,11 +3814,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3862,10 +3840,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119713560</v>
+        <v>119713565</v>
       </c>
       <c r="B32" t="n">
-        <v>87406</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3878,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3902,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463750</v>
+        <v>463746</v>
       </c>
       <c r="R32" t="n">
-        <v>7079623</v>
+        <v>7079435</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3938,6 +3916,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3964,10 +3947,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119713573</v>
+        <v>119713572</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4004,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463554</v>
+        <v>463687</v>
       </c>
       <c r="R33" t="n">
-        <v>7079655</v>
+        <v>7079358</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,7 +4027,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4071,10 +4054,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119713563</v>
+        <v>119713596</v>
       </c>
       <c r="B34" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4087,21 +4070,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4111,10 +4094,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463821</v>
+        <v>463751</v>
       </c>
       <c r="R34" t="n">
-        <v>7079575</v>
+        <v>7079627</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4156,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119713599</v>
+        <v>119713567</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,21 +4172,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4213,10 +4196,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463627</v>
+        <v>463736</v>
       </c>
       <c r="R35" t="n">
-        <v>7079516</v>
+        <v>7079409</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,6 +4232,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4266,7 @@
         <v>119713601</v>
       </c>
       <c r="B36" t="n">
-        <v>90558</v>
+        <v>90576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4377,10 +4365,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119713603</v>
+        <v>119713584</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,21 +4381,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4405,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463681</v>
+        <v>463721</v>
       </c>
       <c r="R37" t="n">
-        <v>7079627</v>
+        <v>7079654</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4453,6 +4441,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4479,10 +4472,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119713591</v>
+        <v>119713578</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4519,10 +4512,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463851</v>
+        <v>463582</v>
       </c>
       <c r="R38" t="n">
-        <v>7079576</v>
+        <v>7079667</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4559,7 +4552,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4586,10 +4579,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119713571</v>
+        <v>119713602</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4602,21 +4595,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4626,10 +4619,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463594</v>
+        <v>463691</v>
       </c>
       <c r="R39" t="n">
-        <v>7079554</v>
+        <v>7079539</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4662,11 +4655,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4693,10 +4681,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119713589</v>
+        <v>119713593</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4709,34 +4697,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupvattsbodarna v, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463830</v>
+        <v>463736</v>
       </c>
       <c r="R40" t="n">
-        <v>7079579</v>
+        <v>7079601</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4769,11 +4769,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,10 +4795,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119713604</v>
+        <v>119713579</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4816,21 +4811,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4840,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463710</v>
+        <v>463762</v>
       </c>
       <c r="R41" t="n">
-        <v>7079569</v>
+        <v>7079557</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4876,6 +4871,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
